--- a/Demo Dokumente/Testprotokoll-Purview-Demos.xlsx
+++ b/Demo Dokumente/Testprotokoll-Purview-Demos.xlsx
@@ -576,12 +576,12 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Finance Team, Leadership</t>
+          <t>Finance Team</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Confidential-Finance; hat über Leadership auch Rechte auf Legal und Strictly-Confidential-Intern — kein Negativtest für Legal</t>
+          <t>Confidential-Finance; zugleich Negativtest für Legal und Strictly-Confidential-Intern</t>
         </is>
       </c>
     </row>
